--- a/_input_data/tsiino_hiiwiida_team.xlsx
+++ b/_input_data/tsiino_hiiwiida_team.xlsx
@@ -1534,55 +1534,6 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF111827"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F2937"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF467886"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>

--- a/_input_data/tsiino_hiiwiida_team.xlsx
+++ b/_input_data/tsiino_hiiwiida_team.xlsx
@@ -250,7 +250,7 @@
     <t xml:space="preserve">claudia@jbrj.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Claudine Massi Mynssen</t>
+    <t xml:space="preserve">Claudine Mynssen</t>
   </si>
   <si>
     <t xml:space="preserve">cmynssen@gmail.com</t>

--- a/_input_data/tsiino_hiiwiida_team.xlsx
+++ b/_input_data/tsiino_hiiwiida_team.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="332">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -55,24 +55,18 @@
     <t xml:space="preserve">Bolsista Comunidade São Jorge </t>
   </si>
   <si>
-    <t xml:space="preserve">Adriel Michel Sierra Pinilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orcid.org/0000-0001-9900-1350</t>
+    <t xml:space="preserve">Alice Lima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allicelima29@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Integrante</t>
   </si>
   <si>
-    <t xml:space="preserve">Alice Lima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allicelima29@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alysson da Matta</t>
   </si>
   <si>
@@ -178,24 +172,6 @@
     <t xml:space="preserve">https://orcid.org/0000-0001-7892-5757</t>
   </si>
   <si>
-    <t xml:space="preserve">Carine Emer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JBRJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c.emer09@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://lattes.cnpq.br/2953372411320303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scholar.google.com.br/citations?user=rlWY7rQAAAAJ&amp;hl=pt-PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orcid.org/0000-0002-1258-2816</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caroline Miranda Biondi</t>
   </si>
   <si>
@@ -244,12 +220,6 @@
     <t xml:space="preserve">FAPEAM</t>
   </si>
   <si>
-    <t xml:space="preserve">Claudia Rabelo Lopes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claudia@jbrj.gov.br</t>
-  </si>
-  <si>
     <t xml:space="preserve">Claudine Mynssen</t>
   </si>
   <si>
@@ -299,9 +269,6 @@
   </si>
   <si>
     <t xml:space="preserve">FACEPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel da Silva Costa</t>
   </si>
   <si>
     <t xml:space="preserve">Danilo Soares Gissi</t>
@@ -374,15 +341,6 @@
     <t xml:space="preserve">https://orcid.org/0000-0001-6623-3788</t>
   </si>
   <si>
-    <t xml:space="preserve">Deivid Andrés Fonseca Cortés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deafonsecaco@unal.edu.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orcid.org/0000-0001-7207-9940</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denilson Peralta</t>
   </si>
   <si>
@@ -425,6 +383,9 @@
     <t xml:space="preserve">Domingos Cardoso</t>
   </si>
   <si>
+    <t xml:space="preserve">JBRJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">domingoscardoso@jbrj.gov.br</t>
   </si>
   <si>
@@ -530,9 +491,6 @@
     <t xml:space="preserve">FAPESQ-PB</t>
   </si>
   <si>
-    <t xml:space="preserve">Fernanda de Paiva Ligabue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Francisco Farroñay</t>
   </si>
   <si>
@@ -584,9 +542,6 @@
     <t xml:space="preserve">Gilfany Macário</t>
   </si>
   <si>
-    <t xml:space="preserve">Giselle Farias Campos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Giulia Cavalcanti Ottino</t>
   </si>
   <si>
@@ -617,15 +572,6 @@
     <t xml:space="preserve">http://lattes.cnpq.br/7585591482247977</t>
   </si>
   <si>
-    <t xml:space="preserve">Henrique Eduardo Mendonça Nascimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hnasci@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orcid.org/0000-0002-8631-2325</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jefferson Guedes de Carvalho Sobrinho</t>
   </si>
   <si>
@@ -698,9 +644,6 @@
     <t xml:space="preserve">https://orcid.org/0000-0002-9696-1978</t>
   </si>
   <si>
-    <t xml:space="preserve">José Roberto Pinho de Andrade Lima</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jovita Yesilyurt</t>
   </si>
   <si>
@@ -708,9 +651,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.nhm.ac.uk/our-science/people/jovita-yesilyurt.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kleuto Moraes da Silva</t>
   </si>
   <si>
     <t xml:space="preserve">Layon O. Demarchi</t>
@@ -879,15 +819,6 @@
     <t xml:space="preserve">Bolsista Comunidade Baniwa – Itacoatiara-mirim</t>
   </si>
   <si>
-    <t xml:space="preserve">Nelcioney José de Souza Araújo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://lattes.cnpq.br/5403024203206579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocírio de Souza Pereira</t>
-  </si>
-  <si>
     <t xml:space="preserve">Onalto Ferreira de Menezes</t>
   </si>
   <si>
@@ -924,15 +855,6 @@
     <t xml:space="preserve">http://lattes.cnpq.br/8375441896375273</t>
   </si>
   <si>
-    <t xml:space="preserve">Rafaela Saraiva Peres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rafaelasaraiva82@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://lattes.cnpq.br/8803152023599223</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renato Vieira Soares</t>
   </si>
   <si>
@@ -958,12 +880,6 @@
   </si>
   <si>
     <t xml:space="preserve">UKRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selma Lúcia de Moura Gonzales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://lattes.cnpq.br/5473538959324771</t>
   </si>
   <si>
     <t xml:space="preserve">Shirley Cunha Feuerstein</t>
@@ -1320,16 +1236,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <u val="single"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1484,11 +1400,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1834,2233 +1750,2124 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="22" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="G6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>13</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H6" s="9"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="22" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="7"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
-        <v>39</v>
+      <c r="G9" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="10" t="s">
-        <v>46</v>
+      <c r="G10" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>66</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>73</v>
       </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H16" s="3" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="A19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="5"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="10" t="s">
+        <v>105</v>
+      </c>
       <c r="H20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>99</v>
+        <v>109</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="17.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>107</v>
+        <v>12</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="13"/>
+        <v>118</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="5"/>
+      <c r="A23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A24" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
-        <v>119</v>
+      <c r="A25" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>101</v>
+      <c r="A26" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>128</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>136</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
+      <c r="A29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" s="13"/>
+      <c r="A30" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="12"/>
       <c r="E30" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>151</v>
+      <c r="A31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="H32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="3" t="s">
-        <v>160</v>
+      <c r="E33" s="15" t="s">
+        <v>170</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>161</v>
+      <c r="G33" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="E34" s="15"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>168</v>
-      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+        <v>173</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="E35" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="H35" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
+      <c r="A36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="10" t="s">
-        <v>185</v>
+      <c r="E39" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B41" s="3"/>
+        <v>200</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="H41" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I42" s="3"/>
+      <c r="A42" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A43" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+        <v>212</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>214</v>
+      </c>
       <c r="H44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+        <v>218</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>221</v>
+      </c>
       <c r="G45" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="3"/>
+        <v>222</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>46</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>227</v>
+      </c>
       <c r="G46" s="3" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>211</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
       <c r="H47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="I47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C49" s="3"/>
+        <v>238</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="12"/>
-      <c r="P50" s="12"/>
+      <c r="A50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
+        <v>243</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="E51" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="H51" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="5"/>
+      <c r="A52" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B53" s="3"/>
+        <v>255</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>256</v>
+      </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>13</v>
+        <v>258</v>
       </c>
       <c r="I53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>231</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>234</v>
-      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>235</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="I54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>243</v>
+        <v>262</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>247</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D57" s="13"/>
+        <v>269</v>
+      </c>
+      <c r="D57" s="3"/>
       <c r="E57" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
+        <v>270</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="I57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="F58" s="13"/>
-      <c r="G58" s="17" t="s">
-        <v>256</v>
-      </c>
+      <c r="A58" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D59" s="3"/>
+        <v>274</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>275</v>
+      </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="F59" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="H59" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I59" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I61" s="3"/>
+      <c r="A61" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>274</v>
-      </c>
+      <c r="A62" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="5"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>276</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="3" t="s">
-        <v>277</v>
-      </c>
+      <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="I63" s="3"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="18"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" s="3"/>
+        <v>120</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="H64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B65" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
+      <c r="G65" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="H65" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
+        <v>303</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>305</v>
+      </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="H66" s="3" t="s">
-        <v>283</v>
+        <v>14</v>
       </c>
       <c r="I66" s="3"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="E67" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="H67" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68" s="3"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="3"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="3"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="11"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="11"/>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="11"/>
+      <c r="T68" s="11"/>
+      <c r="U68" s="11"/>
+      <c r="V68" s="11"/>
+      <c r="W68" s="11"/>
+      <c r="X68" s="11"/>
+      <c r="Y68" s="11"/>
+      <c r="Z68" s="11"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="11"/>
+      <c r="Q69" s="11"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="11"/>
+      <c r="T69" s="11"/>
+      <c r="U69" s="11"/>
+      <c r="V69" s="11"/>
+      <c r="W69" s="11"/>
+      <c r="X69" s="11"/>
+      <c r="Y69" s="11"/>
+      <c r="Z69" s="11"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B70" s="19"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="T70" s="11"/>
+      <c r="U70" s="11"/>
+      <c r="V70" s="11"/>
+      <c r="W70" s="11"/>
+      <c r="X70" s="11"/>
+      <c r="Y70" s="11"/>
+      <c r="Z70" s="11"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B71" s="19"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="11"/>
+      <c r="Q71" s="11"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="11"/>
+      <c r="T71" s="11"/>
+      <c r="U71" s="11"/>
+      <c r="V71" s="11"/>
+      <c r="W71" s="11"/>
+      <c r="X71" s="11"/>
+      <c r="Y71" s="11"/>
+      <c r="Z71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>305</v>
-      </c>
+      <c r="A72" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="11"/>
+      <c r="U72" s="11"/>
+      <c r="V72" s="11"/>
+      <c r="W72" s="11"/>
+      <c r="X72" s="11"/>
+      <c r="Y72" s="11"/>
+      <c r="Z72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="3"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12"/>
-      <c r="O73" s="12"/>
-      <c r="P73" s="12"/>
+      <c r="A73" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="11"/>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="11"/>
+      <c r="T73" s="11"/>
+      <c r="U73" s="11"/>
+      <c r="V73" s="11"/>
+      <c r="W73" s="11"/>
+      <c r="X73" s="11"/>
+      <c r="Y73" s="11"/>
+      <c r="Z73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="3"/>
+      <c r="A74" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="11"/>
+      <c r="U74" s="11"/>
+      <c r="V74" s="11"/>
+      <c r="W74" s="11"/>
+      <c r="X74" s="11"/>
+      <c r="Y74" s="11"/>
+      <c r="Z74" s="11"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="5"/>
+      <c r="A75" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="11"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="11"/>
+      <c r="V75" s="11"/>
+      <c r="W75" s="11"/>
+      <c r="X75" s="11"/>
+      <c r="Y75" s="11"/>
+      <c r="Z75" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="A76" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="G76" s="4" t="s">
+      <c r="B76" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="11"/>
+      <c r="X76" s="11"/>
+      <c r="Y76" s="11"/>
+      <c r="Z76" s="11"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="H76" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="5"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="12"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="3"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="18"/>
-      <c r="P77" s="18"/>
+      <c r="I77" s="20"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3" t="s">
+      <c r="I78" s="20"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="I79" s="20"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="3"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="3"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12"/>
-      <c r="O80" s="12"/>
-      <c r="P80" s="12"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="12"/>
-    </row>
-    <row r="82" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="B82" s="19"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
-      <c r="L82" s="12"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12"/>
-      <c r="S82" s="12"/>
-      <c r="T82" s="12"/>
-      <c r="U82" s="12"/>
-      <c r="V82" s="12"/>
-      <c r="W82" s="12"/>
-      <c r="X82" s="12"/>
-      <c r="Y82" s="12"/>
-      <c r="Z82" s="12"/>
-    </row>
-    <row r="83" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
-      <c r="L83" s="12"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12"/>
-      <c r="O83" s="12"/>
-      <c r="P83" s="12"/>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="12"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12"/>
-      <c r="U83" s="12"/>
-      <c r="V83" s="12"/>
-      <c r="W83" s="12"/>
-      <c r="X83" s="12"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12"/>
-    </row>
-    <row r="84" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
-      <c r="L84" s="12"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12"/>
-      <c r="O84" s="12"/>
-      <c r="P84" s="12"/>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="12"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12"/>
-      <c r="U84" s="12"/>
-      <c r="V84" s="12"/>
-      <c r="W84" s="12"/>
-      <c r="X84" s="12"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12"/>
-    </row>
-    <row r="85" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="12"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="12"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12"/>
-      <c r="U85" s="12"/>
-      <c r="V85" s="12"/>
-      <c r="W85" s="12"/>
-      <c r="X85" s="12"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="12"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="12"/>
-      <c r="V86" s="12"/>
-      <c r="W86" s="12"/>
-      <c r="X86" s="12"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="12"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12"/>
-      <c r="U87" s="12"/>
-      <c r="V87" s="12"/>
-      <c r="W87" s="12"/>
-      <c r="X87" s="12"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I88" s="12"/>
-      <c r="J88" s="12"/>
-      <c r="K88" s="12"/>
-      <c r="L88" s="12"/>
-      <c r="M88" s="12"/>
-      <c r="N88" s="12"/>
-      <c r="O88" s="12"/>
-      <c r="P88" s="12"/>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="12"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12"/>
-      <c r="U88" s="12"/>
-      <c r="V88" s="12"/>
-      <c r="W88" s="12"/>
-      <c r="X88" s="12"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I89" s="12"/>
-      <c r="J89" s="12"/>
-      <c r="K89" s="12"/>
-      <c r="L89" s="12"/>
-      <c r="M89" s="12"/>
-      <c r="N89" s="12"/>
-      <c r="O89" s="12"/>
-      <c r="P89" s="12"/>
-      <c r="Q89" s="12"/>
-      <c r="R89" s="12"/>
-      <c r="S89" s="12"/>
-      <c r="T89" s="12"/>
-      <c r="U89" s="12"/>
-      <c r="V89" s="12"/>
-      <c r="W89" s="12"/>
-      <c r="X89" s="12"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C90" s="12"/>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
-      <c r="K90" s="12"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="12"/>
-      <c r="O90" s="12"/>
-      <c r="P90" s="12"/>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="12"/>
-      <c r="S90" s="12"/>
-      <c r="T90" s="12"/>
-      <c r="U90" s="12"/>
-      <c r="V90" s="12"/>
-      <c r="W90" s="12"/>
-      <c r="X90" s="12"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="20" t="s">
-        <v>350</v>
-      </c>
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="20"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="20"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+    </row>
+    <row r="87" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="20"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+    </row>
+    <row r="88" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+    </row>
+    <row r="89" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="20"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+    </row>
+    <row r="90" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+    </row>
+    <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="20"/>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
       <c r="G91" s="20"/>
-      <c r="H91" s="12" t="s">
-        <v>351</v>
-      </c>
+      <c r="H91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="20" t="s">
-        <v>352</v>
-      </c>
+    <row r="92" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="20"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
       <c r="G92" s="20"/>
-      <c r="H92" s="12" t="s">
-        <v>353</v>
-      </c>
+      <c r="H92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="20" t="s">
-        <v>354</v>
-      </c>
+    <row r="93" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="20"/>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
       <c r="G93" s="20"/>
-      <c r="H93" s="12" t="s">
-        <v>355</v>
-      </c>
+      <c r="H93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="20" t="s">
-        <v>356</v>
-      </c>
+    <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="20"/>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="20"/>
       <c r="G94" s="20"/>
-      <c r="H94" s="12" t="s">
-        <v>357</v>
-      </c>
+      <c r="H94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="20" t="s">
-        <v>358</v>
-      </c>
+    <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="20"/>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20"/>
       <c r="G95" s="20"/>
-      <c r="H95" s="12" t="s">
-        <v>359</v>
-      </c>
+      <c r="H95" s="20"/>
       <c r="I95" s="20"/>
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13897,216 +13704,75 @@
       <c r="H989" s="20"/>
       <c r="I989" s="20"/>
     </row>
-    <row r="990" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A990" s="20"/>
-      <c r="B990" s="20"/>
-      <c r="C990" s="20"/>
-      <c r="D990" s="20"/>
-      <c r="E990" s="20"/>
-      <c r="F990" s="20"/>
-      <c r="G990" s="20"/>
-      <c r="H990" s="20"/>
-      <c r="I990" s="20"/>
-    </row>
-    <row r="991" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A991" s="20"/>
-      <c r="B991" s="20"/>
-      <c r="C991" s="20"/>
-      <c r="D991" s="20"/>
-      <c r="E991" s="20"/>
-      <c r="F991" s="20"/>
-      <c r="G991" s="20"/>
-      <c r="H991" s="20"/>
-      <c r="I991" s="20"/>
-    </row>
-    <row r="992" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A992" s="20"/>
-      <c r="B992" s="20"/>
-      <c r="C992" s="20"/>
-      <c r="D992" s="20"/>
-      <c r="E992" s="20"/>
-      <c r="F992" s="20"/>
-      <c r="G992" s="20"/>
-      <c r="H992" s="20"/>
-      <c r="I992" s="20"/>
-    </row>
-    <row r="993" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A993" s="20"/>
-      <c r="B993" s="20"/>
-      <c r="C993" s="20"/>
-      <c r="D993" s="20"/>
-      <c r="E993" s="20"/>
-      <c r="F993" s="20"/>
-      <c r="G993" s="20"/>
-      <c r="H993" s="20"/>
-      <c r="I993" s="20"/>
-    </row>
-    <row r="994" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A994" s="20"/>
-      <c r="B994" s="20"/>
-      <c r="C994" s="20"/>
-      <c r="D994" s="20"/>
-      <c r="E994" s="20"/>
-      <c r="F994" s="20"/>
-      <c r="G994" s="20"/>
-      <c r="H994" s="20"/>
-      <c r="I994" s="20"/>
-    </row>
-    <row r="995" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A995" s="20"/>
-      <c r="B995" s="20"/>
-      <c r="C995" s="20"/>
-      <c r="D995" s="20"/>
-      <c r="E995" s="20"/>
-      <c r="F995" s="20"/>
-      <c r="G995" s="20"/>
-      <c r="H995" s="20"/>
-      <c r="I995" s="20"/>
-    </row>
-    <row r="996" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="20"/>
-      <c r="B996" s="20"/>
-      <c r="C996" s="20"/>
-      <c r="D996" s="20"/>
-      <c r="E996" s="20"/>
-      <c r="F996" s="20"/>
-      <c r="G996" s="20"/>
-      <c r="H996" s="20"/>
-      <c r="I996" s="20"/>
-    </row>
-    <row r="997" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="20"/>
-      <c r="B997" s="20"/>
-      <c r="C997" s="20"/>
-      <c r="D997" s="20"/>
-      <c r="E997" s="20"/>
-      <c r="F997" s="20"/>
-      <c r="G997" s="20"/>
-      <c r="H997" s="20"/>
-      <c r="I997" s="20"/>
-    </row>
-    <row r="998" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="20"/>
-      <c r="B998" s="20"/>
-      <c r="C998" s="20"/>
-      <c r="D998" s="20"/>
-      <c r="E998" s="20"/>
-      <c r="F998" s="20"/>
-      <c r="G998" s="20"/>
-      <c r="H998" s="20"/>
-      <c r="I998" s="20"/>
-    </row>
-    <row r="999" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="20"/>
-      <c r="B999" s="20"/>
-      <c r="C999" s="20"/>
-      <c r="D999" s="20"/>
-      <c r="E999" s="20"/>
-      <c r="F999" s="20"/>
-      <c r="G999" s="20"/>
-      <c r="H999" s="20"/>
-      <c r="I999" s="20"/>
-    </row>
-    <row r="1000" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="20"/>
-      <c r="B1000" s="20"/>
-      <c r="C1000" s="20"/>
-      <c r="D1000" s="20"/>
-      <c r="E1000" s="20"/>
-      <c r="F1000" s="20"/>
-      <c r="G1000" s="20"/>
-      <c r="H1000" s="20"/>
-      <c r="I1000" s="20"/>
-    </row>
-    <row r="1001" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="20"/>
-      <c r="B1001" s="20"/>
-      <c r="C1001" s="20"/>
-      <c r="D1001" s="20"/>
-      <c r="E1001" s="20"/>
-      <c r="F1001" s="20"/>
-      <c r="G1001" s="20"/>
-      <c r="H1001" s="20"/>
-      <c r="I1001" s="20"/>
-    </row>
-    <row r="1002" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1002" s="20"/>
-      <c r="B1002" s="20"/>
-      <c r="C1002" s="20"/>
-      <c r="D1002" s="20"/>
-      <c r="E1002" s="20"/>
-      <c r="F1002" s="20"/>
-      <c r="G1002" s="20"/>
-      <c r="H1002" s="20"/>
-      <c r="I1002" s="20"/>
-    </row>
-    <row r="1003" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1003" s="20"/>
-      <c r="B1003" s="20"/>
-      <c r="C1003" s="20"/>
-      <c r="D1003" s="20"/>
-      <c r="E1003" s="20"/>
-      <c r="F1003" s="20"/>
-      <c r="G1003" s="20"/>
-      <c r="H1003" s="20"/>
-      <c r="I1003" s="20"/>
-    </row>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" display="https://www.instagram.com/anaflabio?igsh=ZXpqZnZ6djhvZnQ4"/>
-    <hyperlink ref="E6" r:id="rId2" display="https://lattes.cnpq.br/0954834722824284"/>
-    <hyperlink ref="G6" r:id="rId3" display="https://orcid.org/0000-0002-5641-024X"/>
-    <hyperlink ref="G10" r:id="rId4" display="https://orcid.org/0009-0008-3121-7436"/>
-    <hyperlink ref="F12" r:id="rId5" display="https://scholar.google.com.br/citations?user=rlWY7rQAAAAJ&amp;hl=pt-PT"/>
-    <hyperlink ref="F14" r:id="rId6" display="https://scholar.google.es/citations?hl=en&amp;user=6C8ozYwAAAAJ"/>
-    <hyperlink ref="D18" r:id="rId7" display="https://www.instagram.com/cleissa_oliveira99/"/>
-    <hyperlink ref="E18" r:id="rId8" display="http://lattes.cnpq.br/5162929358710284"/>
-    <hyperlink ref="G18" r:id="rId9" display="https://orcid.org/0009-0006-0651-3028"/>
-    <hyperlink ref="F21" r:id="rId10" display="https://scholar.google.com.br/citations?user=yyOMVXIAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="G21" r:id="rId11" display="https://orcid.org/0000-0002-5081-2803"/>
-    <hyperlink ref="E22" r:id="rId12" display="http://lattes.cnpq.br/4816888485402257"/>
-    <hyperlink ref="D23" r:id="rId13" display="https://www.instagram.com/dayrodrigues978?igsh=MXh5bjN6ZXIxYXdvNg=="/>
-    <hyperlink ref="E23" r:id="rId14" display="http://lattes.cnpq.br/2669986623645624"/>
-    <hyperlink ref="G24" r:id="rId15" display="https://orcid.org/0000-0001-6623-3788"/>
-    <hyperlink ref="F27" r:id="rId16" display="https://scholar.google.com/citations?user=QC55kc8AAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="D29" r:id="rId17" display="https://www.uesc.br/centros/cme/index.php?item=conteudo_equipe.php"/>
-    <hyperlink ref="E29" r:id="rId18" display="http://lattes.cnpq.br/2078633938003826"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://scholar.google.com.br/citations?user=11C9o4sAAAAJ&amp;hl=pt-PT"/>
-    <hyperlink ref="G29" r:id="rId20" display="https://orcid.org/0000-0002-1057-0432"/>
-    <hyperlink ref="E30" r:id="rId21" display="http://lattes.cnpq.br/3062370237651162"/>
-    <hyperlink ref="D31" r:id="rId22" display="https://www.instagram.com/bonesfabio/"/>
-    <hyperlink ref="E31" r:id="rId23" display="https://lattes.cnpq.br/7058195011982806"/>
-    <hyperlink ref="F31" r:id="rId24" display="https://scholar.google.com/citations?user=B_ztjnQAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="G31" r:id="rId25" display="https://orcid.org/0000-0003-2956-1859"/>
-    <hyperlink ref="E36" r:id="rId26" display="http://lattes.cnpq.br/3177536756466033"/>
-    <hyperlink ref="E39" r:id="rId27" display="http://lattes.cnpq.br/4435352680317467"/>
-    <hyperlink ref="G39" r:id="rId28" display="https://orcid.org/0009-0000-5487-0915"/>
-    <hyperlink ref="E47" r:id="rId29" display="http://lattes.cnpq.br/6183123558330376"/>
-    <hyperlink ref="F47" r:id="rId30" display="https://scholar.google.com.br/citations?user=ZdlSYoAAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="G47" r:id="rId31" display="https://orcid.org/0000-0002-3193-9315"/>
-    <hyperlink ref="D48" r:id="rId32" display="https://www.nhm.ac.uk/our-science/people/jo-wilbraham.html"/>
-    <hyperlink ref="G48" r:id="rId33" display="https://orcid.org/0000-0003-4101-0611"/>
-    <hyperlink ref="E50" r:id="rId34" display="http://lattes.cnpq.br/8595257513343424"/>
-    <hyperlink ref="G50" r:id="rId35" display="https://orcid.org/0000-0002-9696-1978"/>
-    <hyperlink ref="D52" r:id="rId36" display="https://www.nhm.ac.uk/our-science/people/jovita-yesilyurt.html"/>
-    <hyperlink ref="F54" r:id="rId37" display="https://scholar.google.com.br/citations?user=osGO9nEAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="G54" r:id="rId38" display="https://orcid.org/0000-0001-8441-2106 "/>
-    <hyperlink ref="D55" r:id="rId39" display="https://sigaa.ufpb.br/sigaa/public/docente/portal.jsf?siape=1168469"/>
-    <hyperlink ref="F55" r:id="rId40" display="https://scholar.google.com/citations?user=9P5PzkEAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="F56" r:id="rId41" display="https://scholar.google.com/citations?user=tc_iIMkAAAAJ&amp;hl=en"/>
-    <hyperlink ref="C58" r:id="rId42" display="luizhenrique.vieira@hotmail.com"/>
-    <hyperlink ref="G58" r:id="rId43" display="https://orcid.org/0000-0001-7623-2826"/>
-    <hyperlink ref="D72" r:id="rId44" display="https://www.nhm.ac.uk/our-science/people/sandra-knapp.html"/>
-    <hyperlink ref="F72" r:id="rId45" display="https://scholar.google.com/citations?user=yHApU78AAAAJ&amp;hl=en"/>
-    <hyperlink ref="D75" r:id="rId46" display="https://www.nhm.ac.uk/our-science/people/silvia-pressel.html"/>
-    <hyperlink ref="F75" r:id="rId47" display="https://scholar.google.com/citations?user=uUQ3V7UAAAAJ&amp;hl=en"/>
-    <hyperlink ref="G75" r:id="rId48" display="https://orcid.org/0000-0001-9652-6338"/>
-    <hyperlink ref="D76" r:id="rId49" display="https://www.instagram.com/talesajr/"/>
-    <hyperlink ref="E76" r:id="rId50" display="http://lattes.cnpq.br/8055018980718354"/>
-    <hyperlink ref="F76" r:id="rId51" display="https://scholar.google.com.br/citations?user=YU7MfnAAAAAJ&amp;hl=pt-BR"/>
-    <hyperlink ref="G76" r:id="rId52" display="https://orcid.org/0000-0003-4243-9794"/>
-    <hyperlink ref="F78" r:id="rId53" display="https://scholar.google.com/citations?user=na-OicAAAAAJ&amp;hl=en"/>
+    <hyperlink ref="D5" r:id="rId1" display="https://www.instagram.com/anaflabio?igsh=ZXpqZnZ6djhvZnQ4"/>
+    <hyperlink ref="E5" r:id="rId2" display="https://lattes.cnpq.br/0954834722824284"/>
+    <hyperlink ref="G5" r:id="rId3" display="https://orcid.org/0000-0002-5641-024X"/>
+    <hyperlink ref="G9" r:id="rId4" display="https://orcid.org/0009-0008-3121-7436"/>
+    <hyperlink ref="F12" r:id="rId5" display="https://scholar.google.es/citations?hl=en&amp;user=6C8ozYwAAAAJ"/>
+    <hyperlink ref="D15" r:id="rId6" display="https://www.instagram.com/cleissa_oliveira99/"/>
+    <hyperlink ref="E15" r:id="rId7" display="http://lattes.cnpq.br/5162929358710284"/>
+    <hyperlink ref="G15" r:id="rId8" display="https://orcid.org/0009-0006-0651-3028"/>
+    <hyperlink ref="F17" r:id="rId9" display="https://scholar.google.com.br/citations?user=yyOMVXIAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="G17" r:id="rId10" display="https://orcid.org/0000-0002-5081-2803"/>
+    <hyperlink ref="E18" r:id="rId11" display="http://lattes.cnpq.br/4816888485402257"/>
+    <hyperlink ref="D19" r:id="rId12" display="https://www.instagram.com/dayrodrigues978?igsh=MXh5bjN6ZXIxYXdvNg=="/>
+    <hyperlink ref="E19" r:id="rId13" display="http://lattes.cnpq.br/2669986623645624"/>
+    <hyperlink ref="G20" r:id="rId14" display="https://orcid.org/0000-0001-6623-3788"/>
+    <hyperlink ref="F22" r:id="rId15" display="https://scholar.google.com/citations?user=QC55kc8AAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="D24" r:id="rId16" display="https://www.uesc.br/centros/cme/index.php?item=conteudo_equipe.php"/>
+    <hyperlink ref="E24" r:id="rId17" display="http://lattes.cnpq.br/2078633938003826"/>
+    <hyperlink ref="F24" r:id="rId18" display="https://scholar.google.com.br/citations?user=11C9o4sAAAAJ&amp;hl=pt-PT"/>
+    <hyperlink ref="G24" r:id="rId19" display="https://orcid.org/0000-0002-1057-0432"/>
+    <hyperlink ref="E25" r:id="rId20" display="http://lattes.cnpq.br/3062370237651162"/>
+    <hyperlink ref="D26" r:id="rId21" display="https://www.instagram.com/bonesfabio/"/>
+    <hyperlink ref="E26" r:id="rId22" display="https://lattes.cnpq.br/7058195011982806"/>
+    <hyperlink ref="F26" r:id="rId23" display="https://scholar.google.com/citations?user=B_ztjnQAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="G26" r:id="rId24" display="https://orcid.org/0000-0003-2956-1859"/>
+    <hyperlink ref="E30" r:id="rId25" display="http://lattes.cnpq.br/3177536756466033"/>
+    <hyperlink ref="E33" r:id="rId26" display="http://lattes.cnpq.br/4435352680317467"/>
+    <hyperlink ref="G33" r:id="rId27" display="https://orcid.org/0009-0000-5487-0915"/>
+    <hyperlink ref="E39" r:id="rId28" display="http://lattes.cnpq.br/6183123558330376"/>
+    <hyperlink ref="F39" r:id="rId29" display="https://scholar.google.com.br/citations?user=ZdlSYoAAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="G39" r:id="rId30" display="https://orcid.org/0000-0002-3193-9315"/>
+    <hyperlink ref="D40" r:id="rId31" display="https://www.nhm.ac.uk/our-science/people/jo-wilbraham.html"/>
+    <hyperlink ref="G40" r:id="rId32" display="https://orcid.org/0000-0003-4101-0611"/>
+    <hyperlink ref="E42" r:id="rId33" display="http://lattes.cnpq.br/8595257513343424"/>
+    <hyperlink ref="G42" r:id="rId34" display="https://orcid.org/0000-0002-9696-1978"/>
+    <hyperlink ref="D43" r:id="rId35" display="https://www.nhm.ac.uk/our-science/people/jovita-yesilyurt.html"/>
+    <hyperlink ref="F44" r:id="rId36" display="https://scholar.google.com.br/citations?user=osGO9nEAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="G44" r:id="rId37" display="https://orcid.org/0000-0001-8441-2106 "/>
+    <hyperlink ref="D45" r:id="rId38" display="https://sigaa.ufpb.br/sigaa/public/docente/portal.jsf?siape=1168469"/>
+    <hyperlink ref="F45" r:id="rId39" display="https://scholar.google.com/citations?user=9P5PzkEAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="F46" r:id="rId40" display="https://scholar.google.com/citations?user=tc_iIMkAAAAJ&amp;hl=en"/>
+    <hyperlink ref="C48" r:id="rId41" display="luizhenrique.vieira@hotmail.com"/>
+    <hyperlink ref="G48" r:id="rId42" display="https://orcid.org/0000-0001-7623-2826"/>
+    <hyperlink ref="D59" r:id="rId43" display="https://www.nhm.ac.uk/our-science/people/sandra-knapp.html"/>
+    <hyperlink ref="F59" r:id="rId44" display="https://scholar.google.com/citations?user=yHApU78AAAAJ&amp;hl=en"/>
+    <hyperlink ref="D61" r:id="rId45" display="https://www.nhm.ac.uk/our-science/people/silvia-pressel.html"/>
+    <hyperlink ref="F61" r:id="rId46" display="https://scholar.google.com/citations?user=uUQ3V7UAAAAJ&amp;hl=en"/>
+    <hyperlink ref="G61" r:id="rId47" display="https://orcid.org/0000-0001-9652-6338"/>
+    <hyperlink ref="D62" r:id="rId48" display="https://www.instagram.com/talesajr/"/>
+    <hyperlink ref="E62" r:id="rId49" display="http://lattes.cnpq.br/8055018980718354"/>
+    <hyperlink ref="F62" r:id="rId50" display="https://scholar.google.com.br/citations?user=YU7MfnAAAAAJ&amp;hl=pt-BR"/>
+    <hyperlink ref="G62" r:id="rId51" display="https://orcid.org/0000-0003-4243-9794"/>
+    <hyperlink ref="F64" r:id="rId52" display="https://scholar.google.com/citations?user=na-OicAAAAAJ&amp;hl=en"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
